--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7999,0.0169,0.0298,0.1525</t>
-  </si>
-  <si>
-    <t>0.0290,0.0038,0.0016,0.9850</t>
-  </si>
-  <si>
-    <t>0.8299,0.0283,0.0057,0.1610</t>
-  </si>
-  <si>
-    <t>0.0271,0.0210,0.0017,0.9852</t>
-  </si>
-  <si>
-    <t>0.9977,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0023,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9834,0.0156,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0032,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9849,0.0161,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9893,0.0132,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9938,0.0034,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.7628,0.0417,0.2292,0.0123</t>
-  </si>
-  <si>
-    <t>0.0814,0.0081,0.9506,0.0023</t>
-  </si>
-  <si>
-    <t>0.1255,0.0819,0.8229,0.0030</t>
-  </si>
-  <si>
-    <t>0.0410,0.0420,0.9239,0.0041</t>
-  </si>
-  <si>
-    <t>0.5630,0.0108,0.6025,0.0066</t>
-  </si>
-  <si>
-    <t>0.0181,0.9824,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.0088,0.9862,0.0051,0.0005</t>
-  </si>
-  <si>
-    <t>0.2144,0.8608,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.0229,0.9760,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.0103,0.9871,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.5027,0.0125,0.6622,0.0030</t>
-  </si>
-  <si>
-    <t>0.5928,0.0324,0.4344,0.0160</t>
-  </si>
-  <si>
-    <t>0.2206,0.0068,0.9111,0.0005</t>
-  </si>
-  <si>
-    <t>0.1262,0.0207,0.8821,0.0047</t>
-  </si>
-  <si>
-    <t>0.1807,0.0038,0.9257,0.0010</t>
-  </si>
-  <si>
-    <t>0.0875,0.0154,0.9058,0.0115</t>
-  </si>
-  <si>
-    <t>0.0025,0.0025,0.9945,0.0021</t>
-  </si>
-  <si>
-    <t>0.1177,0.9047,0.0057,0.0016</t>
-  </si>
-  <si>
-    <t>0.1329,0.8559,0.0451,0.0066</t>
-  </si>
-  <si>
-    <t>0.0015,0.0072,0.9909,0.0088</t>
-  </si>
-  <si>
-    <t>0.0173,0.8220,0.5802,0.0006</t>
-  </si>
-  <si>
-    <t>0.5777,0.4980,0.0388,0.0150</t>
-  </si>
-  <si>
-    <t>0.8518,0.1078,0.0229,0.0111</t>
-  </si>
-  <si>
-    <t>0.8533,0.2611,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.0246,0.9533,0.0679,0.0102</t>
-  </si>
-  <si>
-    <t>0.0108,0.9404,0.0685,0.0061</t>
-  </si>
-  <si>
-    <t>0.0120,0.0184,0.9615,0.0262</t>
-  </si>
-  <si>
-    <t>0.0352,0.5601,0.8332,0.0065</t>
-  </si>
-  <si>
-    <t>0.2709,0.0075,0.7817,0.0133</t>
-  </si>
-  <si>
-    <t>0.0315,0.0424,0.9644,0.0012</t>
-  </si>
-  <si>
-    <t>0.0062,0.9735,0.0238,0.0003</t>
-  </si>
-  <si>
-    <t>0.0917,0.0267,0.9171,0.0019</t>
-  </si>
-  <si>
-    <t>0.0412,0.1601,0.0081,0.9576</t>
-  </si>
-  <si>
-    <t>0.0018,0.9932,0.0037,0.0031</t>
-  </si>
-  <si>
-    <t>0.0011,0.9954,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.0036,0.9778,0.0277,0.0209</t>
-  </si>
-  <si>
-    <t>0.0735,0.0872,0.8857,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.4168,0.9793,0.0015</t>
-  </si>
-  <si>
-    <t>0.4726,0.0080,0.6842,0.0034</t>
-  </si>
-  <si>
-    <t>0.0256,0.0023,0.9841,0.0010</t>
-  </si>
-  <si>
-    <t>0.0094,0.0253,0.9765,0.0027</t>
-  </si>
-  <si>
-    <t>0.0009,0.0114,0.9921,0.0013</t>
-  </si>
-  <si>
-    <t>0.8934,0.1433,0.0080,0.0020</t>
-  </si>
-  <si>
-    <t>0.9727,0.0147,0.0083,0.0002</t>
-  </si>
-  <si>
-    <t>0.9895,0.0035,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.0557,0.1239,0.9328,0.0009</t>
-  </si>
-  <si>
-    <t>0.9671,0.0383,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.9931,0.0067,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9928,0.0031,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.0021,0.9488,0.7789,0.0004</t>
-  </si>
-  <si>
-    <t>0.0078,0.0927,0.9733,0.0013</t>
-  </si>
-  <si>
-    <t>0.0114,0.0243,0.9586,0.0224</t>
-  </si>
-  <si>
-    <t>0.0016,0.7858,0.9518,0.0009</t>
-  </si>
-  <si>
-    <t>0.0011,0.0071,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0174,0.9092,0.1058,0.0006</t>
-  </si>
-  <si>
-    <t>0.0258,0.9622,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.6608,0.0112,0.5907,0.0022</t>
-  </si>
-  <si>
-    <t>0.6749,0.1178,0.1095,0.1527</t>
-  </si>
-  <si>
-    <t>0.2626,0.2307,0.2493,0.0008</t>
-  </si>
-  <si>
-    <t>0.0046,0.9523,0.4402,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.9586,0.4433,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.9828,0.5289,0.0007</t>
-  </si>
-  <si>
-    <t>0.0013,0.9817,0.4501,0.0004</t>
-  </si>
-  <si>
-    <t>0.0961,0.0006,0.0094,0.9084</t>
-  </si>
-  <si>
-    <t>0.0075,0.0048,0.0004,0.9949</t>
-  </si>
-  <si>
-    <t>0.0032,0.0004,0.0002,0.9976</t>
-  </si>
-  <si>
-    <t>0.0607,0.0044,0.0035,0.9675</t>
-  </si>
-  <si>
-    <t>0.0326,0.0034,0.0104,0.9758</t>
-  </si>
-  <si>
-    <t>0.0065,0.0030,0.0019,0.9951</t>
-  </si>
-  <si>
-    <t>0.0010,0.9727,0.7703,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.8868,0.8902,0.0016</t>
-  </si>
-  <si>
-    <t>0.0083,0.9216,0.4595,0.0014</t>
-  </si>
-  <si>
-    <t>0.0045,0.6971,0.9250,0.0009</t>
-  </si>
-  <si>
-    <t>0.0018,0.9729,0.3072,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.9339,0.6850,0.0004</t>
-  </si>
-  <si>
-    <t>0.9835,0.0170,0.0059,0.0004</t>
-  </si>
-  <si>
-    <t>0.9486,0.0694,0.0063,0.0007</t>
-  </si>
-  <si>
-    <t>0.9745,0.0360,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9913,0.0085,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9862,0.0154,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9908,0.0057,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9916,0.0072,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9873,0.0150,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9955,0.0009,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9966,0.0021,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9921,0.0017,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9938,0.0036,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0082,0.0059,0.9905,0.0024</t>
-  </si>
-  <si>
-    <t>0.0368,0.0594,0.9384,0.0043</t>
-  </si>
-  <si>
-    <t>0.8132,0.0267,0.1691,0.0045</t>
-  </si>
-  <si>
-    <t>0.0955,0.0362,0.8819,0.0035</t>
-  </si>
-  <si>
-    <t>0.0342,0.9744,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.0267,0.9737,0.0077,0.0007</t>
-  </si>
-  <si>
-    <t>0.1477,0.9083,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.5516,0.5823,0.0148,0.0019</t>
-  </si>
-  <si>
-    <t>0.0289,0.9631,0.0193,0.0009</t>
-  </si>
-  <si>
-    <t>0.0453,0.9526,0.0057,0.0002</t>
-  </si>
-  <si>
-    <t>0.3030,0.7699,0.0110,0.0005</t>
-  </si>
-  <si>
-    <t>0.8589,0.0351,0.1013,0.0065</t>
-  </si>
-  <si>
-    <t>0.2195,0.0201,0.8368,0.0091</t>
-  </si>
-  <si>
-    <t>0.7698,0.0097,0.3038,0.0073</t>
-  </si>
-  <si>
-    <t>0.5587,0.1847,0.2765,0.0312</t>
-  </si>
-  <si>
-    <t>0.0167,0.0590,0.0049,0.9830</t>
-  </si>
-  <si>
-    <t>0.0010,0.9949,0.0099,0.0014</t>
-  </si>
-  <si>
-    <t>0.0016,0.9928,0.0204,0.0012</t>
-  </si>
-  <si>
-    <t>0.1177,0.8706,0.0105,0.0212</t>
-  </si>
-  <si>
-    <t>0.0050,0.9802,0.2312,0.0015</t>
-  </si>
-  <si>
-    <t>0.0252,0.9653,0.0325,0.0004</t>
-  </si>
-  <si>
-    <t>0.7649,0.3106,0.0122,0.0010</t>
-  </si>
-  <si>
-    <t>0.1165,0.9072,0.0096,0.0018</t>
-  </si>
-  <si>
-    <t>0.9902,0.0036,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9804,0.0030,0.0002,0.0070</t>
-  </si>
-  <si>
-    <t>0.9851,0.0118,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9764,0.0091,0.0057,0.0039</t>
-  </si>
-  <si>
-    <t>0.9888,0.0118,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9361,0.0373,0.0465,0.0020</t>
-  </si>
-  <si>
-    <t>0.9828,0.0049,0.0020,0.0042</t>
-  </si>
-  <si>
-    <t>0.9745,0.0122,0.0010,0.0045</t>
-  </si>
-  <si>
-    <t>0.0009,0.8339,0.9685,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.8667,0.9473,0.0001</t>
-  </si>
-  <si>
-    <t>0.0233,0.2126,0.9288,0.0015</t>
-  </si>
-  <si>
-    <t>0.0300,0.0930,0.9233,0.0038</t>
-  </si>
-  <si>
-    <t>0.6818,0.0216,0.2666,0.0519</t>
-  </si>
-  <si>
-    <t>0.7771,0.0696,0.1171,0.0095</t>
-  </si>
-  <si>
-    <t>0.3691,0.0313,0.7626,0.0010</t>
-  </si>
-  <si>
-    <t>0.4697,0.0746,0.5088,0.0113</t>
-  </si>
-  <si>
-    <t>0.1572,0.0052,0.0007,0.9444</t>
-  </si>
-  <si>
-    <t>0.0015,0.0029,0.0006,0.9981</t>
-  </si>
-  <si>
-    <t>0.0053,0.0179,0.0040,0.9907</t>
-  </si>
-  <si>
-    <t>0.0231,0.0004,0.0031,0.9856</t>
-  </si>
-  <si>
-    <t>0.0013,0.9380,0.9106,0.0005</t>
-  </si>
-  <si>
-    <t>0.9786,0.0236,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.1499,0.8550,0.0197,0.0072</t>
-  </si>
-  <si>
-    <t>0.9788,0.0055,0.0003,0.0070</t>
-  </si>
-  <si>
-    <t>0.6798,0.4188,0.0124,0.0015</t>
-  </si>
-  <si>
-    <t>0.9823,0.0092,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.5801,0.0067,0.0641,0.3661</t>
-  </si>
-  <si>
-    <t>0.9671,0.0101,0.0008,0.0093</t>
-  </si>
-  <si>
-    <t>0.0475,0.1041,0.7177,0.2692</t>
-  </si>
-  <si>
-    <t>0.9001,0.0013,0.0061,0.1045</t>
-  </si>
-  <si>
-    <t>0.9579,0.0103,0.0051,0.0117</t>
-  </si>
-  <si>
-    <t>0.3816,0.7194,0.0072,0.0040</t>
-  </si>
-  <si>
-    <t>0.9443,0.0236,0.0130,0.0030</t>
-  </si>
-  <si>
-    <t>0.6574,0.3027,0.0792,0.0073</t>
-  </si>
-  <si>
-    <t>0.2797,0.7096,0.0082,0.0140</t>
-  </si>
-  <si>
-    <t>0.7997,0.2147,0.0160,0.0013</t>
-  </si>
-  <si>
-    <t>0.7243,0.2101,0.0704,0.0299</t>
-  </si>
-  <si>
-    <t>0.9900,0.0028,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9776,0.0047,0.0011,0.0131</t>
-  </si>
-  <si>
-    <t>0.9962,0.0008,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9918,0.0017,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9892,0.0090,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9915,0.0087,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9868,0.0025,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.9933,0.0047,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.4571,0.6792,0.0038,0.0026</t>
-  </si>
-  <si>
-    <t>0.3116,0.6255,0.0417,0.0006</t>
-  </si>
-  <si>
-    <t>0.3888,0.6910,0.0094,0.0019</t>
-  </si>
-  <si>
-    <t>0.6377,0.3028,0.1278,0.0023</t>
-  </si>
-  <si>
-    <t>0.9248,0.1513,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9395,0.0434,0.0177,0.0012</t>
-  </si>
-  <si>
-    <t>0.9727,0.0555,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.6577,0.4311,0.0043,0.0073</t>
-  </si>
-  <si>
-    <t>0.0024,0.0093,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.9572,0.0216,0.0195,0.0029</t>
-  </si>
-  <si>
-    <t>0.0016,0.0006,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0073,0.1359,0.9770,0.0010</t>
-  </si>
-  <si>
-    <t>0.5407,0.0097,0.6159,0.0071</t>
-  </si>
-  <si>
-    <t>0.0632,0.1062,0.8582,0.0047</t>
-  </si>
-  <si>
-    <t>0.0136,0.0154,0.9836,0.0004</t>
-  </si>
-  <si>
-    <t>0.0052,0.0008,0.9959,0.0002</t>
-  </si>
-  <si>
-    <t>0.0076,0.0267,0.9823,0.0042</t>
-  </si>
-  <si>
-    <t>0.3688,0.0542,0.5767,0.0722</t>
-  </si>
-  <si>
-    <t>0.2221,0.0207,0.8712,0.0026</t>
-  </si>
-  <si>
-    <t>0.5786,0.1370,0.2966,0.0168</t>
-  </si>
-  <si>
-    <t>0.2201,0.2369,0.5126,0.0017</t>
-  </si>
-  <si>
-    <t>0.3584,0.2128,0.4196,0.0075</t>
-  </si>
-  <si>
-    <t>0.2637,0.1306,0.6172,0.0137</t>
-  </si>
-  <si>
-    <t>0.6190,0.0307,0.4837,0.0115</t>
-  </si>
-  <si>
-    <t>0.3329,0.1667,0.5168,0.0225</t>
-  </si>
-  <si>
-    <t>0.5865,0.6074,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.2974,0.8221,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.7872,0.1803,0.0423,0.0018</t>
-  </si>
-  <si>
-    <t>0.9850,0.0090,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.8400,0.2837,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.6273,0.0743,0.3406,0.0121</t>
-  </si>
-  <si>
-    <t>0.8261,0.0047,0.2626,0.0093</t>
-  </si>
-  <si>
-    <t>0.4185,0.0236,0.0369,0.6473</t>
-  </si>
-  <si>
-    <t>0.6136,0.0103,0.5775,0.0027</t>
-  </si>
-  <si>
-    <t>0.8631,0.0057,0.2652,0.0018</t>
-  </si>
-  <si>
-    <t>0.1085,0.0084,0.9038,0.0078</t>
-  </si>
-  <si>
-    <t>0.0244,0.2806,0.7992,0.0246</t>
-  </si>
-  <si>
-    <t>0.0206,0.1309,0.9348,0.0026</t>
-  </si>
-  <si>
-    <t>0.2069,0.2095,0.7247,0.0143</t>
-  </si>
-  <si>
-    <t>0.0169,0.1838,0.9256,0.0034</t>
-  </si>
-  <si>
-    <t>0.9795,0.0146,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9753,0.0261,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.9918,0.0048,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9796,0.0220,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9835,0.0122,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9870,0.0116,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0035,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9895,0.0073,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.7336,0.0379,0.3536,0.0051</t>
-  </si>
-  <si>
-    <t>0.3632,0.4563,0.2556,0.0036</t>
-  </si>
-  <si>
-    <t>0.8758,0.0231,0.0056,0.0750</t>
-  </si>
-  <si>
-    <t>0.0171,0.0284,0.9729,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0073,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0409,0.0887,0.9003,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9986,0.0021</t>
-  </si>
-  <si>
-    <t>0.1233,0.0564,0.8830,0.0015</t>
-  </si>
-  <si>
-    <t>0.0099,0.0058,0.9933,0.0004</t>
-  </si>
-  <si>
-    <t>0.0325,0.0290,0.9266,0.0056</t>
-  </si>
-  <si>
-    <t>0.1797,0.0640,0.8202,0.0058</t>
-  </si>
-  <si>
-    <t>0.8269,0.0033,0.1435,0.0194</t>
-  </si>
-  <si>
-    <t>0.6976,0.0103,0.4743,0.0045</t>
-  </si>
-  <si>
-    <t>0.8091,0.0071,0.2710,0.0064</t>
-  </si>
-  <si>
-    <t>0.9871,0.0146,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9954,0.0035,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9867,0.0089,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9842,0.0190,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9715,0.0453,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9911,0.0036,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.0203,0.1187,0.9048,0.0008</t>
-  </si>
-  <si>
-    <t>0.0026,0.0669,0.9897,0.0006</t>
-  </si>
-  <si>
-    <t>0.0048,0.2759,0.9538,0.0005</t>
-  </si>
-  <si>
-    <t>0.0789,0.0297,0.9329,0.0007</t>
-  </si>
-  <si>
-    <t>0.0023,0.0063,0.9918,0.0021</t>
-  </si>
-  <si>
-    <t>0.3606,0.0127,0.1891,0.3966</t>
-  </si>
-  <si>
-    <t>0.1191,0.0727,0.6786,0.2031</t>
-  </si>
-  <si>
-    <t>0.1114,0.0074,0.6057,0.1805</t>
-  </si>
-  <si>
-    <t>0.2117,0.0048,0.0003,0.9221</t>
-  </si>
-  <si>
-    <t>0.0238,0.1034,0.0010,0.9750</t>
-  </si>
-  <si>
-    <t>0.0760,0.0027,0.0041,0.9610</t>
-  </si>
-  <si>
-    <t>0.0024,0.0017,0.0045,0.9957</t>
-  </si>
-  <si>
-    <t>0.0039,0.0007,0.0005,0.9967</t>
-  </si>
-  <si>
-    <t>0.3493,0.0957,0.0042,0.7151</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.6123,0.0698,0.0143,0.3394</t>
+  </si>
+  <si>
+    <t>0.0087,0.0046,0.0003,0.9941</t>
+  </si>
+  <si>
+    <t>0.3272,0.0508,0.0014,0.6986</t>
+  </si>
+  <si>
+    <t>0.0793,0.0011,0.0022,0.9738</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9932,0.0090,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0051,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9935,0.0098,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0052,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0016,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.4649,0.4142,0.1301,0.0254</t>
+  </si>
+  <si>
+    <t>0.2160,0.0781,0.7177,0.0031</t>
+  </si>
+  <si>
+    <t>0.4781,0.0113,0.7064,0.0028</t>
+  </si>
+  <si>
+    <t>0.2485,0.0144,0.8230,0.0030</t>
+  </si>
+  <si>
+    <t>0.4814,0.0500,0.5453,0.0016</t>
+  </si>
+  <si>
+    <t>0.0763,0.9421,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.9952,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.1266,0.9018,0.0072,0.0024</t>
+  </si>
+  <si>
+    <t>0.0352,0.9650,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.9942,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.5474,0.0456,0.4480,0.0361</t>
+  </si>
+  <si>
+    <t>0.3272,0.1218,0.5543,0.0095</t>
+  </si>
+  <si>
+    <t>0.0078,0.0035,0.9923,0.0009</t>
+  </si>
+  <si>
+    <t>0.2024,0.0128,0.8610,0.0017</t>
+  </si>
+  <si>
+    <t>0.2732,0.0014,0.9134,0.0008</t>
+  </si>
+  <si>
+    <t>0.0149,0.0052,0.9810,0.0030</t>
+  </si>
+  <si>
+    <t>0.0025,0.0017,0.9951,0.0025</t>
+  </si>
+  <si>
+    <t>0.3405,0.6591,0.0575,0.0038</t>
+  </si>
+  <si>
+    <t>0.4042,0.2638,0.2711,0.0010</t>
+  </si>
+  <si>
+    <t>0.0168,0.0449,0.9725,0.0030</t>
+  </si>
+  <si>
+    <t>0.0348,0.8410,0.3745,0.0029</t>
+  </si>
+  <si>
+    <t>0.8712,0.1404,0.0114,0.0057</t>
+  </si>
+  <si>
+    <t>0.8129,0.1776,0.0287,0.0051</t>
+  </si>
+  <si>
+    <t>0.6341,0.5394,0.0042,0.0017</t>
+  </si>
+  <si>
+    <t>0.0286,0.9523,0.0391,0.0011</t>
+  </si>
+  <si>
+    <t>0.0151,0.9180,0.1628,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.0414,0.9471,0.0631</t>
+  </si>
+  <si>
+    <t>0.0148,0.2415,0.9592,0.0016</t>
+  </si>
+  <si>
+    <t>0.0411,0.0133,0.9516,0.0011</t>
+  </si>
+  <si>
+    <t>0.0249,0.1257,0.9047,0.0002</t>
+  </si>
+  <si>
+    <t>0.0201,0.9404,0.0502,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0232,0.9805,0.0066</t>
+  </si>
+  <si>
+    <t>0.0842,0.7882,0.0245,0.3545</t>
+  </si>
+  <si>
+    <t>0.0038,0.9712,0.0610,0.0496</t>
+  </si>
+  <si>
+    <t>0.0014,0.9938,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.9876,0.0483,0.0060</t>
+  </si>
+  <si>
+    <t>0.0075,0.0960,0.9615,0.0025</t>
+  </si>
+  <si>
+    <t>0.0025,0.5268,0.9723,0.0002</t>
+  </si>
+  <si>
+    <t>0.0756,0.0215,0.8754,0.0450</t>
+  </si>
+  <si>
+    <t>0.0452,0.0091,0.9575,0.0050</t>
+  </si>
+  <si>
+    <t>0.0021,0.0016,0.9953,0.0028</t>
+  </si>
+  <si>
+    <t>0.0117,0.0140,0.9805,0.0009</t>
+  </si>
+  <si>
+    <t>0.9425,0.0825,0.0031,0.0013</t>
+  </si>
+  <si>
+    <t>0.9731,0.0115,0.0016,0.0057</t>
+  </si>
+  <si>
+    <t>0.9703,0.0260,0.0030,0.0016</t>
+  </si>
+  <si>
+    <t>0.0156,0.2149,0.9569,0.0001</t>
+  </si>
+  <si>
+    <t>0.9896,0.0068,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9888,0.0099,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9690,0.0329,0.0049,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9660,0.9042,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0721,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.0140,0.0118,0.9797,0.0058</t>
+  </si>
+  <si>
+    <t>0.0008,0.8010,0.9810,0.0001</t>
+  </si>
+  <si>
+    <t>0.0349,0.0045,0.9786,0.0010</t>
+  </si>
+  <si>
+    <t>0.1559,0.7205,0.1062,0.0013</t>
+  </si>
+  <si>
+    <t>0.0234,0.9695,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.6880,0.0208,0.5341,0.0033</t>
+  </si>
+  <si>
+    <t>0.6850,0.2083,0.1274,0.0208</t>
+  </si>
+  <si>
+    <t>0.0503,0.0695,0.9550,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.8284,0.8719,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9710,0.7385,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9940,0.0305,0.0011</t>
+  </si>
+  <si>
+    <t>0.0018,0.9780,0.3706,0.0005</t>
+  </si>
+  <si>
+    <t>0.0671,0.0046,0.0806,0.8600</t>
+  </si>
+  <si>
+    <t>0.0106,0.0207,0.0006,0.9926</t>
+  </si>
+  <si>
+    <t>0.0045,0.0035,0.0002,0.9973</t>
+  </si>
+  <si>
+    <t>0.0063,0.0235,0.0002,0.9950</t>
+  </si>
+  <si>
+    <t>0.0379,0.0012,0.0037,0.9750</t>
+  </si>
+  <si>
+    <t>0.0350,0.0051,0.0112,0.9724</t>
+  </si>
+  <si>
+    <t>0.0013,0.9494,0.9064,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.8082,0.9614,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.9638,0.2314,0.0011</t>
+  </si>
+  <si>
+    <t>0.0040,0.4595,0.9581,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9337,0.8250,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.9613,0.3519,0.0027</t>
+  </si>
+  <si>
+    <t>0.9889,0.0128,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9918,0.0068,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9845,0.0188,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9914,0.0038,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9895,0.0065,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9877,0.0109,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9863,0.0255,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0016,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0023,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0013,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9961,0.0011,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0008,0.9941,0.0139</t>
+  </si>
+  <si>
+    <t>0.0986,0.0291,0.9102,0.0013</t>
+  </si>
+  <si>
+    <t>0.8474,0.0122,0.1542,0.0077</t>
+  </si>
+  <si>
+    <t>0.0702,0.0114,0.9377,0.0016</t>
+  </si>
+  <si>
+    <t>0.0782,0.9328,0.0012,0.0033</t>
+  </si>
+  <si>
+    <t>0.0341,0.9619,0.0113,0.0006</t>
+  </si>
+  <si>
+    <t>0.0795,0.9395,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.1089,0.9161,0.0027,0.0024</t>
+  </si>
+  <si>
+    <t>0.0088,0.9889,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.0197,0.9781,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.6671,0.4752,0.0062,0.0010</t>
+  </si>
+  <si>
+    <t>0.6272,0.0633,0.3499,0.0156</t>
+  </si>
+  <si>
+    <t>0.1808,0.0373,0.8500,0.0016</t>
+  </si>
+  <si>
+    <t>0.8456,0.0227,0.1320,0.0068</t>
+  </si>
+  <si>
+    <t>0.8549,0.0087,0.1727,0.0038</t>
+  </si>
+  <si>
+    <t>0.0897,0.0171,0.0193,0.9468</t>
+  </si>
+  <si>
+    <t>0.0010,0.9967,0.0070,0.0005</t>
+  </si>
+  <si>
+    <t>0.0043,0.9708,0.0363,0.0612</t>
+  </si>
+  <si>
+    <t>0.0149,0.8341,0.0027,0.5014</t>
+  </si>
+  <si>
+    <t>0.0018,0.9733,0.6258,0.0008</t>
+  </si>
+  <si>
+    <t>0.0703,0.9188,0.0295,0.0023</t>
+  </si>
+  <si>
+    <t>0.3628,0.7224,0.0124,0.0016</t>
+  </si>
+  <si>
+    <t>0.8597,0.1916,0.0099,0.0013</t>
+  </si>
+  <si>
+    <t>0.9726,0.0164,0.0098,0.0022</t>
+  </si>
+  <si>
+    <t>0.9737,0.0213,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9691,0.0311,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9928,0.0025,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9527,0.0411,0.0090,0.0028</t>
+  </si>
+  <si>
+    <t>0.9927,0.0033,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9812,0.0095,0.0085,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9100,0.9873,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9530,0.7343,0.0001</t>
+  </si>
+  <si>
+    <t>0.0472,0.0137,0.9585,0.0012</t>
+  </si>
+  <si>
+    <t>0.0493,0.1323,0.8792,0.0036</t>
+  </si>
+  <si>
+    <t>0.8588,0.0292,0.0757,0.0083</t>
+  </si>
+  <si>
+    <t>0.3300,0.0141,0.7899,0.0034</t>
+  </si>
+  <si>
+    <t>0.1387,0.0078,0.8968,0.0073</t>
+  </si>
+  <si>
+    <t>0.5372,0.1263,0.3300,0.0160</t>
+  </si>
+  <si>
+    <t>0.0212,0.0076,0.0009,0.9852</t>
+  </si>
+  <si>
+    <t>0.0012,0.0021,0.0002,0.9987</t>
+  </si>
+  <si>
+    <t>0.0248,0.0022,0.0089,0.9728</t>
+  </si>
+  <si>
+    <t>0.0065,0.0006,0.0019,0.9948</t>
+  </si>
+  <si>
+    <t>0.0026,0.9212,0.6302,0.0011</t>
+  </si>
+  <si>
+    <t>0.9045,0.1289,0.0070,0.0025</t>
+  </si>
+  <si>
+    <t>0.0927,0.9180,0.0025,0.0058</t>
+  </si>
+  <si>
+    <t>0.9014,0.0924,0.0050,0.0051</t>
+  </si>
+  <si>
+    <t>0.4316,0.5869,0.0521,0.0029</t>
+  </si>
+  <si>
+    <t>0.9828,0.0043,0.0086,0.0015</t>
+  </si>
+  <si>
+    <t>0.4139,0.0043,0.0034,0.7914</t>
+  </si>
+  <si>
+    <t>0.9853,0.0050,0.0020,0.0022</t>
+  </si>
+  <si>
+    <t>0.0812,0.2131,0.7952,0.0791</t>
+  </si>
+  <si>
+    <t>0.9326,0.0013,0.0131,0.0249</t>
+  </si>
+  <si>
+    <t>0.9805,0.0010,0.0006,0.0128</t>
+  </si>
+  <si>
+    <t>0.1838,0.8760,0.0058,0.0025</t>
+  </si>
+  <si>
+    <t>0.8614,0.0675,0.0400,0.0052</t>
+  </si>
+  <si>
+    <t>0.4891,0.3567,0.2394,0.0211</t>
+  </si>
+  <si>
+    <t>0.6592,0.1287,0.2208,0.0071</t>
+  </si>
+  <si>
+    <t>0.7659,0.1831,0.0460,0.0038</t>
+  </si>
+  <si>
+    <t>0.9629,0.0076,0.0061,0.0028</t>
+  </si>
+  <si>
+    <t>0.9925,0.0054,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9916,0.0049,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9938,0.0017,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9883,0.0087,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9926,0.0039,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9933,0.0009,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9927,0.0035,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.7610,0.3809,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.7868,0.3577,0.0070,0.0009</t>
+  </si>
+  <si>
+    <t>0.8092,0.2189,0.0189,0.0007</t>
+  </si>
+  <si>
+    <t>0.6201,0.1047,0.4681,0.0118</t>
+  </si>
+  <si>
+    <t>0.9287,0.0700,0.0047,0.0055</t>
+  </si>
+  <si>
+    <t>0.8916,0.1160,0.0132,0.0057</t>
+  </si>
+  <si>
+    <t>0.9531,0.0328,0.0107,0.0018</t>
+  </si>
+  <si>
+    <t>0.8114,0.2198,0.0032,0.0102</t>
+  </si>
+  <si>
+    <t>0.0032,0.0404,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.9484,0.0596,0.0061,0.0011</t>
+  </si>
+  <si>
+    <t>0.0032,0.0176,0.9857,0.0029</t>
+  </si>
+  <si>
+    <t>0.0045,0.0237,0.9850,0.0025</t>
+  </si>
+  <si>
+    <t>0.0140,0.0375,0.9536,0.0050</t>
+  </si>
+  <si>
+    <t>0.0129,0.0947,0.9629,0.0003</t>
+  </si>
+  <si>
+    <t>0.0136,0.0034,0.9889,0.0006</t>
+  </si>
+  <si>
+    <t>0.0122,0.0035,0.9889,0.0001</t>
+  </si>
+  <si>
+    <t>0.0177,0.0227,0.9815,0.0003</t>
+  </si>
+  <si>
+    <t>0.3362,0.0244,0.7349,0.0052</t>
+  </si>
+  <si>
+    <t>0.1590,0.0444,0.8769,0.0039</t>
+  </si>
+  <si>
+    <t>0.2919,0.0552,0.7148,0.0114</t>
+  </si>
+  <si>
+    <t>0.1286,0.6616,0.1820,0.0021</t>
+  </si>
+  <si>
+    <t>0.2672,0.1976,0.5027,0.0018</t>
+  </si>
+  <si>
+    <t>0.3887,0.3015,0.2961,0.0093</t>
+  </si>
+  <si>
+    <t>0.5226,0.2103,0.2576,0.0040</t>
+  </si>
+  <si>
+    <t>0.1282,0.0330,0.8733,0.0029</t>
+  </si>
+  <si>
+    <t>0.2406,0.8233,0.0126,0.0031</t>
+  </si>
+  <si>
+    <t>0.8477,0.3092,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.3701,0.6759,0.0334,0.0009</t>
+  </si>
+  <si>
+    <t>0.9685,0.0333,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.3990,0.6995,0.0060,0.0016</t>
+  </si>
+  <si>
+    <t>0.6796,0.0933,0.1805,0.0071</t>
+  </si>
+  <si>
+    <t>0.8199,0.0069,0.2011,0.0149</t>
+  </si>
+  <si>
+    <t>0.7735,0.0482,0.0377,0.0492</t>
+  </si>
+  <si>
+    <t>0.6116,0.0144,0.5243,0.0056</t>
+  </si>
+  <si>
+    <t>0.8811,0.0047,0.0910,0.0185</t>
+  </si>
+  <si>
+    <t>0.0638,0.0114,0.9303,0.0090</t>
+  </si>
+  <si>
+    <t>0.0218,0.1549,0.9420,0.0052</t>
+  </si>
+  <si>
+    <t>0.1768,0.0265,0.8525,0.0046</t>
+  </si>
+  <si>
+    <t>0.1061,0.0453,0.9005,0.0050</t>
+  </si>
+  <si>
+    <t>0.0368,0.0579,0.9457,0.0009</t>
+  </si>
+  <si>
+    <t>0.9905,0.0051,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9896,0.0063,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9843,0.0075,0.0026,0.0025</t>
+  </si>
+  <si>
+    <t>0.9906,0.0057,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9843,0.0193,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9863,0.0085,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9873,0.0037,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9948,0.0039,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0335,0.0209,0.9680,0.0020</t>
+  </si>
+  <si>
+    <t>0.3123,0.2991,0.5177,0.0136</t>
+  </si>
+  <si>
+    <t>0.8587,0.0753,0.0687,0.0089</t>
+  </si>
+  <si>
+    <t>0.0038,0.0101,0.9942,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.1631,0.9889,0.0012</t>
+  </si>
+  <si>
+    <t>0.0126,0.0871,0.9385,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0078,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.2261,0.1660,0.5215,0.0053</t>
+  </si>
+  <si>
+    <t>0.0036,0.0022,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0481,0.0151,0.9450,0.0007</t>
+  </si>
+  <si>
+    <t>0.2424,0.0515,0.7955,0.0048</t>
+  </si>
+  <si>
+    <t>0.8575,0.0035,0.2446,0.0026</t>
+  </si>
+  <si>
+    <t>0.6108,0.0237,0.3853,0.0467</t>
+  </si>
+  <si>
+    <t>0.8528,0.0030,0.1533,0.0103</t>
+  </si>
+  <si>
+    <t>0.9923,0.0071,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0065,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9918,0.0085,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9802,0.0398,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0020,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9895,0.0099,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0016,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0131,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0095,0.5447,0.4715,0.0134</t>
+  </si>
+  <si>
+    <t>0.0004,0.0332,0.9910,0.0016</t>
+  </si>
+  <si>
+    <t>0.0338,0.1254,0.8726,0.0057</t>
+  </si>
+  <si>
+    <t>0.0990,0.4556,0.4867,0.0071</t>
+  </si>
+  <si>
+    <t>0.0079,0.0044,0.9866,0.0038</t>
+  </si>
+  <si>
+    <t>0.0417,0.0537,0.8932,0.0794</t>
+  </si>
+  <si>
+    <t>0.1842,0.0145,0.8564,0.0061</t>
+  </si>
+  <si>
+    <t>0.1358,0.0421,0.7705,0.0631</t>
+  </si>
+  <si>
+    <t>0.6503,0.0220,0.0525,0.3069</t>
+  </si>
+  <si>
+    <t>0.0285,0.0065,0.0002,0.9902</t>
+  </si>
+  <si>
+    <t>0.0547,0.0156,0.0402,0.9310</t>
+  </si>
+  <si>
+    <t>0.0026,0.0055,0.0015,0.9970</t>
+  </si>
+  <si>
+    <t>0.0092,0.0005,0.0001,0.9974</t>
+  </si>
+  <si>
+    <t>0.5444,0.1553,0.0096,0.2908</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2511,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3659,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4191,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5031,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5381,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
